--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484151_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484151_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3592</v>
+        <v>1.2573</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6523</v>
+        <v>2.4482</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2931</v>
+        <v>-1.1909</v>
       </c>
       <c r="G2" t="n">
         <v>0.8302</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4079</v>
+        <v>0.3061</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5667</v>
+        <v>-0.7708</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9746</v>
+        <v>1.0768</v>
       </c>
       <c r="V2" t="n">
         <v>-1.6644</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9695</v>
+        <v>0.9516</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9763</v>
+        <v>2.8743</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0068</v>
+        <v>-1.9227</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8126</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4427</v>
+        <v>-0.4605</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7537</v>
+        <v>-0.8558</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3111</v>
+        <v>0.3953</v>
       </c>
       <c r="V3" t="n">
         <v>2.0263</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3316</v>
+        <v>1.1275</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7221</v>
+        <v>-0.6099</v>
       </c>
       <c r="G4" t="n">
         <v>2.6816</v>
@@ -766,13 +766,13 @@
         <v>2.7774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2256</v>
+        <v>-0.3174</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6914</v>
+        <v>-0.8955</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4658</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4579</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3533</v>
+        <v>-0.6825</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0554</v>
+        <v>0.2507</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2979</v>
+        <v>-0.9332</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3382</v>
@@ -844,13 +844,13 @@
         <v>2.7774</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3609</v>
+        <v>-0.6901</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3716</v>
+        <v>-1.0655</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0107</v>
+        <v>0.3754</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2413</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4893</v>
+        <v>-1.2352</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3558</v>
+        <v>-0.2392</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1335</v>
+        <v>-0.996</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7177</v>
+        <v>-3.6399</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2472</v>
+        <v>1.2095</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4704</v>
+        <v>-4.8493</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0806</v>
+        <v>-1.3971</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0806</v>
+        <v>2.0013</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-3.3984</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7983</v>
+        <v>-2.2427</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3279</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4704</v>
+        <v>-1.4509</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1786</v>
+        <v>-0.4747</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4364</v>
+        <v>-0.6518</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2579</v>
+        <v>0.1771</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3866</v>
+        <v>1.689</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3866</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7836</v>
+        <v>-1.6296</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6473</v>
+        <v>-0.3558</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1363</v>
+        <v>-1.2738</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.6399</v>
+        <v>-1.7177</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2095</v>
+        <v>-0.2472</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.8493</v>
+        <v>-1.4704</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3971</v>
+        <v>0.0806</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0013</v>
+        <v>0.0806</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.3984</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2427</v>
+        <v>-1.7983</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.3279</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4509</v>
+        <v>-1.4704</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0231</v>
+        <v>-0.3188</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0599</v>
+        <v>-0.4364</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0368</v>
+        <v>0.1176</v>
       </c>
       <c r="V7" t="n">
-        <v>1.689</v>
+        <v>-0.3866</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1206</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5242</v>
+        <v>-2.2258</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1043</v>
+        <v>-0.0023</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4199</v>
+        <v>-2.2235</v>
       </c>
       <c r="G8" t="n">
         <v>-2.8078</v>
@@ -1078,13 +1078,13 @@
         <v>2.3806</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0026</v>
+        <v>-0.7042</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3092</v>
+        <v>-1.2072</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3066</v>
+        <v>0.503</v>
       </c>
       <c r="V8" t="n">
         <v>0.096</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4613</v>
+        <v>-3.1909</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.7926</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5666</v>
+        <v>-2.3983</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3274</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.721</v>
+        <v>-0.4506</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5611</v>
+        <v>-0.4591</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1599</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2065</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6868</v>
+        <v>-4.0388</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3656</v>
+        <v>-2.7737</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3212</v>
+        <v>-1.2651</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4239</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1338</v>
+        <v>-0.2182</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0567</v>
+        <v>-0.3514</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0771</v>
+        <v>0.1332</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2027</v>
+        <v>-4.2869</v>
       </c>
       <c r="E11" t="n">
         <v>-4.1127</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09</v>
+        <v>-0.1742</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2219</v>
@@ -1312,13 +1312,13 @@
         <v>1.1903</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1298</v>
+        <v>-0.214</v>
       </c>
       <c r="T11" t="n">
         <v>-0.5611</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4313</v>
+        <v>0.3471</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0494</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.5631</v>
+        <v>-14.5632</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.575599999999999</v>
+        <v>-1.575600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.9874</v>
+        <v>-12.9876</v>
       </c>
       <c r="G12" t="n">
         <v>-16.7776</v>
@@ -1390,13 +1390,13 @@
         <v>17.8546</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5426</v>
+        <v>-3.5424</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.2544</v>
+        <v>-7.2546</v>
       </c>
       <c r="U12" t="n">
-        <v>3.712</v>
+        <v>3.7121</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1947999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.239</v>
+        <v>5.67</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7329</v>
+        <v>3.6308</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5062</v>
+        <v>2.0392</v>
       </c>
       <c r="G13" t="n">
         <v>7.4711</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3077</v>
+        <v>0.1233</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.255</v>
+        <v>-0.357</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0527</v>
+        <v>0.4803</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3373</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TROUVE CASELLAS</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4422</v>
+        <v>4.2203</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8599</v>
+        <v>2.4455</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4177</v>
+        <v>1.7748</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1528</v>
+        <v>3.0234</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7789</v>
+        <v>0.3326</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9317</v>
+        <v>2.6908</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5332</v>
+        <v>1.7188</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1651</v>
+        <v>0.3884</v>
       </c>
       <c r="L14" t="n">
-        <v>1.368</v>
+        <v>1.3304</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3803</v>
+        <v>1.3046</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.944</v>
+        <v>-0.0558</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5637</v>
+        <v>1.3604</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4635</v>
+        <v>0.3953</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4252</v>
+        <v>-0.357</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0383</v>
+        <v>0.7524</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6194</v>
+        <v>0.6032</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8854</v>
+        <v>2.0757</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>A. TROUVE CASELLAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0443</v>
+        <v>3.6617</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2415</v>
+        <v>4.2477</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8029</v>
+        <v>-0.5861</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0234</v>
+        <v>0.1528</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3326</v>
+        <v>-1.7789</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6908</v>
+        <v>1.9317</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7188</v>
+        <v>2.5332</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3884</v>
+        <v>1.1651</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3304</v>
+        <v>1.368</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3046</v>
+        <v>-2.3803</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0558</v>
+        <v>-2.944</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3604</v>
+        <v>0.5637</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2193</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5611</v>
+        <v>-0.187</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7804</v>
+        <v>0.87</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6032</v>
+        <v>3.6194</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0757</v>
+        <v>3.8854</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6568</v>
+        <v>2.7665</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6723</v>
+        <v>1.9784</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9846</v>
+        <v>0.7882</v>
       </c>
       <c r="G16" t="n">
         <v>1.2101</v>
@@ -1702,13 +1702,13 @@
         <v>1.3887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1808</v>
+        <v>0.2905</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9352</v>
+        <v>-0.6291</v>
       </c>
       <c r="U16" t="n">
-        <v>1.116</v>
+        <v>0.9196</v>
       </c>
       <c r="V16" t="n">
         <v>0.8692</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>O. BESORA TOMAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9076</v>
+        <v>1.4069</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2831</v>
+        <v>3.6129</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6245000000000001</v>
+        <v>-2.206</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1627</v>
+        <v>3.2172</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4463</v>
+        <v>-5.0094</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2837</v>
+        <v>8.226599999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3859</v>
+        <v>3.8404</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5053</v>
+        <v>-2.8768</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1194</v>
+        <v>6.7172</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2233</v>
+        <v>-0.6232</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.059</v>
+        <v>-2.1327</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8357</v>
+        <v>1.5094</v>
       </c>
       <c r="P17" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2689</v>
+        <v>0.214</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6746</v>
+        <v>-0.442</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5943</v>
+        <v>0.656</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.532</v>
+        <v>-3.0162</v>
       </c>
       <c r="W17" t="n">
         <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7384</v>
+        <v>-4.2226</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2581</v>
+        <v>1.3321</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1828</v>
+        <v>0.2848</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0753</v>
+        <v>1.0472</v>
       </c>
       <c r="G18" t="n">
         <v>0.6193</v>
@@ -1858,13 +1858,13 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1547</v>
+        <v>-0.0808</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.5214</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4687</v>
+        <v>0.4407</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. BESORA TOMAS</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8739</v>
+        <v>0.6604</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6129</v>
+        <v>0.5689</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.7391</v>
+        <v>0.0915</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2172</v>
+        <v>1.1627</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.0094</v>
+        <v>1.4463</v>
       </c>
       <c r="I19" t="n">
-        <v>8.226599999999999</v>
+        <v>-0.2837</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8404</v>
+        <v>1.3859</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.8768</v>
+        <v>2.5053</v>
       </c>
       <c r="L19" t="n">
-        <v>6.7172</v>
+        <v>-1.1194</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6232</v>
+        <v>-0.2233</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1327</v>
+        <v>-1.059</v>
       </c>
       <c r="O19" t="n">
-        <v>1.5094</v>
+        <v>0.8357</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.9919</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.9838</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.3191</v>
+        <v>1.0216</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.442</v>
+        <v>-0.0396</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1229</v>
+        <v>1.0612</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.0162</v>
+        <v>-0.532</v>
       </c>
       <c r="W19" t="n">
         <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.2226</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5867</v>
+        <v>0.4924</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2929</v>
+        <v>-0.1909</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8796</v>
+        <v>0.6832</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1779</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3678</v>
+        <v>0.2735</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4364</v>
+        <v>-0.3344</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8043</v>
+        <v>0.6079</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7548</v>
+        <v>-2.3084</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.878</v>
+        <v>-2.5719</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1232</v>
+        <v>0.2635</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0158</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1049</v>
+        <v>0.3415</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6858</v>
+        <v>-0.3797</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5809</v>
+        <v>0.7212</v>
       </c>
       <c r="V21" t="n">
         <v>1.1352</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6907</v>
+        <v>-3.3387</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4268</v>
+        <v>-1.0187</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2639</v>
+        <v>-2.32</v>
       </c>
       <c r="G22" t="n">
         <v>0.1147</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.2806</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8728</v>
+        <v>-0.4647</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8014</v>
+        <v>0.7453</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1469</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.5631</v>
+        <v>14.5632</v>
       </c>
       <c r="E23" t="n">
-        <v>12.9877</v>
+        <v>12.9875</v>
       </c>
       <c r="F23" t="n">
-        <v>1.575600000000001</v>
+        <v>1.5755</v>
       </c>
       <c r="G23" t="n">
         <v>16.7776</v>
@@ -2248,13 +2248,13 @@
         <v>11.903</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5424</v>
+        <v>3.5425</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.712000000000001</v>
+        <v>-3.7119</v>
       </c>
       <c r="U23" t="n">
-        <v>7.2545</v>
+        <v>7.2546</v>
       </c>
       <c r="V23" t="n">
         <v>0.1945999999999999</v>
